--- a/output/factor_reg_Placebo_HighGrowth_Median.xlsx
+++ b/output/factor_reg_Placebo_HighGrowth_Median.xlsx
@@ -594,58 +594,58 @@
         <v>31</v>
       </c>
       <c r="B2">
-        <v>-0.009673646807904607</v>
+        <v>0.001542087194519092</v>
       </c>
       <c r="C2">
-        <v>-1.5307170164676</v>
+        <v>0.22272042012781</v>
       </c>
       <c r="D2">
-        <v>0.1258393463420936</v>
+        <v>0.8237531075505238</v>
       </c>
       <c r="E2">
-        <v>0.006319683327378338</v>
+        <v>0.006923869816849985</v>
       </c>
       <c r="F2">
-        <v>0.6001846038385521</v>
+        <v>0.5155516050256458</v>
       </c>
       <c r="G2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H2">
-        <v>1.377800805944176</v>
+        <v>1.404444993600394</v>
       </c>
       <c r="I2">
-        <v>0.1684215827803426</v>
+        <v>0.1654703802004966</v>
       </c>
       <c r="J2">
-        <v>8.180666534532691</v>
+        <v>8.487591506701445</v>
       </c>
       <c r="K2">
-        <v>2.822780735630427E-16</v>
+        <v>2.109636131484582E-17</v>
       </c>
       <c r="L2">
-        <v>0.3951323125886495</v>
+        <v>0.01270579300521617</v>
       </c>
       <c r="M2">
-        <v>0.2596103309402861</v>
+        <v>0.2969602547972069</v>
       </c>
       <c r="N2">
-        <v>1.522020757639014</v>
+        <v>0.04278617357024059</v>
       </c>
       <c r="O2">
-        <v>0.1280038796182416</v>
+        <v>0.9658719857893789</v>
       </c>
       <c r="P2">
-        <v>0.2868030562675997</v>
+        <v>0.3979260037979953</v>
       </c>
       <c r="Q2">
-        <v>0.2413437535130591</v>
+        <v>0.2803819467756301</v>
       </c>
       <c r="R2">
-        <v>1.188359143722693</v>
+        <v>1.419228336111196</v>
       </c>
       <c r="S2">
-        <v>0.2346919455999793</v>
+        <v>0.15583245732434</v>
       </c>
     </row>
     <row r="3" spans="1:31">
@@ -653,70 +653,70 @@
         <v>32</v>
       </c>
       <c r="B3">
-        <v>-0.01057336532758106</v>
+        <v>0.001591537866553741</v>
       </c>
       <c r="C3">
-        <v>-1.678138477308003</v>
+        <v>0.2133860577410745</v>
       </c>
       <c r="D3">
-        <v>0.0933200687555365</v>
+        <v>0.8310258543964952</v>
       </c>
       <c r="E3">
-        <v>0.006300651269579609</v>
+        <v>0.007458490415924617</v>
       </c>
       <c r="F3">
-        <v>0.6066603138999249</v>
+        <v>0.5155677965698919</v>
       </c>
       <c r="G3">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H3">
-        <v>1.437040047474942</v>
+        <v>1.401320610959901</v>
       </c>
       <c r="I3">
-        <v>0.1857072479813199</v>
+        <v>0.1662044319092013</v>
       </c>
       <c r="J3">
-        <v>7.738201190830702</v>
+        <v>8.431307124983608</v>
       </c>
       <c r="K3">
-        <v>1.008332004245594E-14</v>
+        <v>3.418253222870626E-17</v>
       </c>
       <c r="L3">
-        <v>0.4818860221149797</v>
+        <v>0.008243079676251985</v>
       </c>
       <c r="M3">
-        <v>0.2542748253548536</v>
+        <v>0.3373277870413018</v>
       </c>
       <c r="N3">
-        <v>1.895138543276878</v>
+        <v>0.02443640871851069</v>
       </c>
       <c r="O3">
-        <v>0.0580740495043045</v>
+        <v>0.9805045070315163</v>
       </c>
       <c r="P3">
-        <v>0.3385381630526744</v>
+        <v>0.395235837570656</v>
       </c>
       <c r="Q3">
-        <v>0.2373234214883422</v>
+        <v>0.2424776026429964</v>
       </c>
       <c r="R3">
-        <v>1.426484419150784</v>
+        <v>1.629989051617967</v>
       </c>
       <c r="S3">
-        <v>0.1537285612144065</v>
+        <v>0.1031038109376647</v>
       </c>
       <c r="T3">
-        <v>0.2247479413815458</v>
+        <v>-0.01182034714937993</v>
       </c>
       <c r="U3">
-        <v>0.1537356126608683</v>
+        <v>0.2491740441718242</v>
       </c>
       <c r="V3">
-        <v>1.461912028654848</v>
+        <v>-0.0474381157502461</v>
       </c>
       <c r="W3">
-        <v>0.1437653183148872</v>
+        <v>0.9621640512256705</v>
       </c>
     </row>
     <row r="4" spans="1:31">
@@ -724,82 +724,82 @@
         <v>33</v>
       </c>
       <c r="B4">
-        <v>-0.00753976451122686</v>
+        <v>0.000320402592597099</v>
       </c>
       <c r="C4">
-        <v>-1.20563493595686</v>
+        <v>0.04959479486795405</v>
       </c>
       <c r="D4">
-        <v>0.2279582824220089</v>
+        <v>0.9604452946231372</v>
       </c>
       <c r="E4">
-        <v>0.006253770761248617</v>
+        <v>0.006460407658710348</v>
       </c>
       <c r="F4">
-        <v>0.6158322649307153</v>
+        <v>0.5209280416649391</v>
       </c>
       <c r="G4">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H4">
-        <v>1.355370257229681</v>
+        <v>1.361928379105537</v>
       </c>
       <c r="I4">
-        <v>0.1562927765659341</v>
+        <v>0.1605578154656238</v>
       </c>
       <c r="J4">
-        <v>8.671995513867527</v>
+        <v>8.482479505316467</v>
       </c>
       <c r="K4">
-        <v>4.246123940455503E-18</v>
+        <v>2.204449436731382E-17</v>
       </c>
       <c r="L4">
-        <v>0.1437532311684535</v>
+        <v>0.1778573787481279</v>
       </c>
       <c r="M4">
-        <v>0.3055362202059693</v>
+        <v>0.3171142038778458</v>
       </c>
       <c r="N4">
-        <v>0.4704948927873298</v>
+        <v>0.5608622274662904</v>
       </c>
       <c r="O4">
-        <v>0.6380014822234175</v>
+        <v>0.5748914616412502</v>
       </c>
       <c r="P4">
-        <v>0.56470610785793</v>
+        <v>0.3715344009161483</v>
       </c>
       <c r="Q4">
-        <v>0.3894034030617254</v>
+        <v>0.2491334465887997</v>
       </c>
       <c r="R4">
-        <v>1.450182775542968</v>
+        <v>1.491306791614271</v>
       </c>
       <c r="S4">
-        <v>0.1470075569780243</v>
+        <v>0.1358809666494135</v>
       </c>
       <c r="X4">
-        <v>-0.3800334602527096</v>
+        <v>0.3945195711191367</v>
       </c>
       <c r="Y4">
-        <v>0.3686553801876686</v>
+        <v>0.5948143139745962</v>
       </c>
       <c r="Z4">
-        <v>-1.030863729858625</v>
+        <v>0.6632650927361278</v>
       </c>
       <c r="AA4">
-        <v>0.3026047273578168</v>
+        <v>0.5071607889340648</v>
       </c>
       <c r="AB4">
-        <v>-0.5581060050300907</v>
+        <v>-0.04166175127050864</v>
       </c>
       <c r="AC4">
-        <v>0.5285296791595633</v>
+        <v>0.3914577964295783</v>
       </c>
       <c r="AD4">
-        <v>-1.055959631098783</v>
+        <v>-0.1064271848727975</v>
       </c>
       <c r="AE4">
-        <v>0.2909866585409935</v>
+        <v>0.9152434251505349</v>
       </c>
     </row>
     <row r="5" spans="1:31">
@@ -807,58 +807,58 @@
         <v>34</v>
       </c>
       <c r="B5">
-        <v>-0.005923596086009164</v>
+        <v>-0.004524747532939105</v>
       </c>
       <c r="C5">
-        <v>-0.6321105428658752</v>
+        <v>-0.7473176945686474</v>
       </c>
       <c r="D5">
-        <v>0.5273146465293613</v>
+        <v>0.4548718140027654</v>
       </c>
       <c r="E5">
-        <v>0.009371139514858663</v>
+        <v>0.006054650606862447</v>
       </c>
       <c r="F5">
-        <v>0.4332034040577194</v>
+        <v>0.6453595440729321</v>
       </c>
       <c r="G5">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H5">
-        <v>1.356288312008948</v>
+        <v>1.347154296879495</v>
       </c>
       <c r="I5">
-        <v>0.2133222188411907</v>
+        <v>0.1429310611082372</v>
       </c>
       <c r="J5">
-        <v>6.357932705634601</v>
+        <v>9.425203216390715</v>
       </c>
       <c r="K5">
-        <v>2.044870110091908E-10</v>
+        <v>4.292735022941672E-21</v>
       </c>
       <c r="L5">
-        <v>1.345125924905524</v>
+        <v>0.4988312173350788</v>
       </c>
       <c r="M5">
-        <v>0.5835525561298367</v>
+        <v>0.2204794556328898</v>
       </c>
       <c r="N5">
-        <v>2.305063889748848</v>
+        <v>2.262483894035278</v>
       </c>
       <c r="O5">
-        <v>0.0211629954955913</v>
+        <v>0.02366752282026219</v>
       </c>
       <c r="P5">
-        <v>0.2710978742702292</v>
+        <v>0.4513912987407659</v>
       </c>
       <c r="Q5">
-        <v>0.2201868349494856</v>
+        <v>0.1519749736171108</v>
       </c>
       <c r="R5">
-        <v>1.231217453724804</v>
+        <v>2.970168627092586</v>
       </c>
       <c r="S5">
-        <v>0.2182415452275569</v>
+        <v>0.002976363217623903</v>
       </c>
     </row>
     <row r="6" spans="1:31">
@@ -866,70 +866,70 @@
         <v>35</v>
       </c>
       <c r="B6">
-        <v>-0.007711997994931879</v>
+        <v>-0.003624952130049191</v>
       </c>
       <c r="C6">
-        <v>-0.8848659904993362</v>
+        <v>-0.6118779897166976</v>
       </c>
       <c r="D6">
-        <v>0.3762289127112654</v>
+        <v>0.540618485064986</v>
       </c>
       <c r="E6">
-        <v>0.008715441747941904</v>
+        <v>0.005924305484051749</v>
       </c>
       <c r="F6">
-        <v>0.446139396783763</v>
+        <v>0.6514494136326879</v>
       </c>
       <c r="G6">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H6">
-        <v>1.474040220322252</v>
+        <v>1.290303600596734</v>
       </c>
       <c r="I6">
-        <v>0.1883835069488965</v>
+        <v>0.15819980937623</v>
       </c>
       <c r="J6">
-        <v>7.824677670546397</v>
+        <v>8.15616406672236</v>
       </c>
       <c r="K6">
-        <v>5.089592615756304E-15</v>
+        <v>3.458325936116936E-16</v>
       </c>
       <c r="L6">
-        <v>1.517569301728267</v>
+        <v>0.4176285001090302</v>
       </c>
       <c r="M6">
-        <v>0.7327906169152654</v>
+        <v>0.2243167140125139</v>
       </c>
       <c r="N6">
-        <v>2.070945324213599</v>
+        <v>1.861780571936036</v>
       </c>
       <c r="O6">
-        <v>0.03836390588392038</v>
+        <v>0.06263402607241161</v>
       </c>
       <c r="P6">
-        <v>0.3739335519952931</v>
+        <v>0.4024415250611557</v>
       </c>
       <c r="Q6">
-        <v>0.255714620278911</v>
+        <v>0.1476365736051815</v>
       </c>
       <c r="R6">
-        <v>1.462308066654301</v>
+        <v>2.725893152582834</v>
       </c>
       <c r="S6">
-        <v>0.1436568090105101</v>
+        <v>0.006412775368085225</v>
       </c>
       <c r="T6">
-        <v>0.4467393285820356</v>
+        <v>-0.2150808793510013</v>
       </c>
       <c r="U6">
-        <v>0.5141854457120316</v>
+        <v>0.1931673340910179</v>
       </c>
       <c r="V6">
-        <v>0.868829198312686</v>
+        <v>-1.113443328102556</v>
       </c>
       <c r="W6">
-        <v>0.3849405601178523</v>
+        <v>0.2655180750987874</v>
       </c>
     </row>
     <row r="7" spans="1:31">
@@ -937,82 +937,82 @@
         <v>36</v>
       </c>
       <c r="B7">
-        <v>-0.00455305960181355</v>
+        <v>-0.003180140203751469</v>
       </c>
       <c r="C7">
-        <v>-0.5663327820249671</v>
+        <v>-0.5165056941627364</v>
       </c>
       <c r="D7">
-        <v>0.5711675794796707</v>
+        <v>0.6055012629949135</v>
       </c>
       <c r="E7">
-        <v>0.008039548029576763</v>
+        <v>0.006157028353591579</v>
       </c>
       <c r="F7">
-        <v>0.473888585474718</v>
+        <v>0.6516503793278088</v>
       </c>
       <c r="G7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H7">
-        <v>1.563817852706345</v>
+        <v>1.331048726737147</v>
       </c>
       <c r="I7">
-        <v>0.1977321260389674</v>
+        <v>0.1505822898075551</v>
       </c>
       <c r="J7">
-        <v>7.908769728183473</v>
+        <v>8.839344443747233</v>
       </c>
       <c r="K7">
-        <v>2.599449228122301E-15</v>
+        <v>9.628186098317782E-19</v>
       </c>
       <c r="L7">
-        <v>1.121908494576138</v>
+        <v>0.3469793467044124</v>
       </c>
       <c r="M7">
-        <v>0.696138297126172</v>
+        <v>0.2580510522460779</v>
       </c>
       <c r="N7">
-        <v>1.61161725939752</v>
+        <v>1.344615120474426</v>
       </c>
       <c r="O7">
-        <v>0.1070452525600221</v>
+        <v>0.1787495578561639</v>
       </c>
       <c r="P7">
-        <v>-0.09650313961856691</v>
+        <v>0.6277508681080836</v>
       </c>
       <c r="Q7">
-        <v>0.7239045779373479</v>
+        <v>0.2804781079386379</v>
       </c>
       <c r="R7">
-        <v>-0.1333091992504556</v>
+        <v>2.238145688880006</v>
       </c>
       <c r="S7">
-        <v>0.8939488525877556</v>
+        <v>0.02521155602684465</v>
       </c>
       <c r="X7">
-        <v>-0.9257228405583375</v>
+        <v>-0.2262876939336791</v>
       </c>
       <c r="Y7">
-        <v>0.7034867613957869</v>
+        <v>0.2931505507644858</v>
       </c>
       <c r="Z7">
-        <v>-1.315906554832123</v>
+        <v>-0.7719163185726924</v>
       </c>
       <c r="AA7">
-        <v>0.1882054084325202</v>
+        <v>0.4401639915599062</v>
       </c>
       <c r="AB7">
-        <v>1.120280641046963</v>
+        <v>-0.3569242563675515</v>
       </c>
       <c r="AC7">
-        <v>1.418618471646357</v>
+        <v>0.4324375621446073</v>
       </c>
       <c r="AD7">
-        <v>0.7896983321716072</v>
+        <v>-0.8253775518422609</v>
       </c>
       <c r="AE7">
-        <v>0.4297039656113296</v>
+        <v>0.4091572753983439</v>
       </c>
     </row>
     <row r="8" spans="1:31">
@@ -1020,58 +1020,58 @@
         <v>37</v>
       </c>
       <c r="B8">
-        <v>-0.003750050721895444</v>
+        <v>0.006066834727458198</v>
       </c>
       <c r="C8">
-        <v>-0.4821920697647001</v>
+        <v>0.7730012658079788</v>
       </c>
       <c r="D8">
-        <v>0.6296695098092313</v>
+        <v>0.4395216315121885</v>
       </c>
       <c r="E8">
-        <v>0.007777089166409128</v>
+        <v>0.007848414997246925</v>
       </c>
       <c r="F8">
-        <v>0.06612002081356605</v>
+        <v>0.02918529223128341</v>
       </c>
       <c r="G8">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H8">
-        <v>0.02151249393522777</v>
+        <v>0.05729069672089962</v>
       </c>
       <c r="I8">
-        <v>0.1582849115713869</v>
+        <v>0.1321582338950412</v>
       </c>
       <c r="J8">
-        <v>0.1359099469536336</v>
+        <v>0.4335007742794093</v>
       </c>
       <c r="K8">
-        <v>0.891892471912316</v>
+        <v>0.6646510036997894</v>
       </c>
       <c r="L8">
-        <v>-0.9499936123168747</v>
+        <v>-0.4861254243298626</v>
       </c>
       <c r="M8">
-        <v>0.5422830371766446</v>
+        <v>0.2893472990218005</v>
       </c>
       <c r="N8">
-        <v>-1.751840915517004</v>
+        <v>-1.680075901773793</v>
       </c>
       <c r="O8">
-        <v>0.079801166532268</v>
+        <v>0.09294254887537004</v>
       </c>
       <c r="P8">
-        <v>0.01570518199737057</v>
+        <v>-0.05346529494277047</v>
       </c>
       <c r="Q8">
-        <v>0.2395348530778061</v>
+        <v>0.2350152235790027</v>
       </c>
       <c r="R8">
-        <v>0.06556533128926</v>
+        <v>-0.2274971558376412</v>
       </c>
       <c r="S8">
-        <v>0.947723891320526</v>
+        <v>0.8200371805767345</v>
       </c>
     </row>
     <row r="9" spans="1:31">
@@ -1079,70 +1079,70 @@
         <v>38</v>
       </c>
       <c r="B9">
-        <v>-0.002861367332649181</v>
+        <v>0.005216489996602934</v>
       </c>
       <c r="C9">
-        <v>-0.4081484811580354</v>
+        <v>0.6569862882348551</v>
       </c>
       <c r="D9">
-        <v>0.6831646687390809</v>
+        <v>0.5111897331207602</v>
       </c>
       <c r="E9">
-        <v>0.007010603897215674</v>
+        <v>0.0079400287190441</v>
       </c>
       <c r="F9">
-        <v>0.07147928588377617</v>
+        <v>0.03664721723722308</v>
       </c>
       <c r="G9">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H9">
-        <v>-0.03700017284730988</v>
+        <v>0.1110170103631673</v>
       </c>
       <c r="I9">
-        <v>0.1259677928276487</v>
+        <v>0.1500006694845482</v>
       </c>
       <c r="J9">
-        <v>-0.2937272458042838</v>
+        <v>0.7401100991392801</v>
       </c>
       <c r="K9">
-        <v>0.7689663330557327</v>
+        <v>0.459233191253072</v>
       </c>
       <c r="L9">
-        <v>-1.035683279613288</v>
+        <v>-0.4093854204327781</v>
       </c>
       <c r="M9">
-        <v>0.6995132135471358</v>
+        <v>0.3269228989815347</v>
       </c>
       <c r="N9">
-        <v>-1.480577149302841</v>
+        <v>-1.252238438200993</v>
       </c>
       <c r="O9">
-        <v>0.1387192882534475</v>
+        <v>0.2104829935468513</v>
       </c>
       <c r="P9">
-        <v>-0.03539538894261864</v>
+        <v>-0.007205687490499491</v>
       </c>
       <c r="Q9">
-        <v>0.2326521361600556</v>
+        <v>0.2099200389856553</v>
       </c>
       <c r="R9">
-        <v>-0.1521386802065208</v>
+        <v>-0.03432586772238493</v>
       </c>
       <c r="S9">
-        <v>0.8790775568922611</v>
+        <v>0.9726172975612517</v>
       </c>
       <c r="T9">
-        <v>-0.2219913872004895</v>
+        <v>0.2032605322016214</v>
       </c>
       <c r="U9">
-        <v>0.5507154405561451</v>
+        <v>0.2651577431221517</v>
       </c>
       <c r="V9">
-        <v>-0.4030963558535956</v>
+        <v>0.766564573254737</v>
       </c>
       <c r="W9">
-        <v>0.6868773413321159</v>
+        <v>0.4433404455072066</v>
       </c>
     </row>
     <row r="10" spans="1:31">
@@ -1150,82 +1150,82 @@
         <v>39</v>
       </c>
       <c r="B10">
-        <v>-0.002986704909413309</v>
+        <v>0.003500542796348572</v>
       </c>
       <c r="C10">
-        <v>-0.4045903860858756</v>
+        <v>0.475281774021086</v>
       </c>
       <c r="D10">
-        <v>0.6857786265051058</v>
+        <v>0.6345861481344088</v>
       </c>
       <c r="E10">
-        <v>0.00738204616849045</v>
+        <v>0.007365194685949118</v>
       </c>
       <c r="F10">
-        <v>0.1632020165118176</v>
+        <v>0.05339324368142273</v>
       </c>
       <c r="G10">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H10">
-        <v>-0.2084475954766637</v>
+        <v>0.03087965236839034</v>
       </c>
       <c r="I10">
-        <v>0.1538984058794314</v>
+        <v>0.1663679193923457</v>
       </c>
       <c r="J10">
-        <v>-1.35444934783774</v>
+        <v>0.1856106182079901</v>
       </c>
       <c r="K10">
-        <v>0.1755930629029301</v>
+        <v>0.8527501261407905</v>
       </c>
       <c r="L10">
-        <v>-0.9781552634076839</v>
+        <v>-0.1691219679562845</v>
       </c>
       <c r="M10">
-        <v>0.7036106670629614</v>
+        <v>0.2825823273420483</v>
       </c>
       <c r="N10">
-        <v>-1.390193908643735</v>
+        <v>-0.5984874197443102</v>
       </c>
       <c r="O10">
-        <v>0.1644700026812195</v>
+        <v>0.5495147505945437</v>
       </c>
       <c r="P10">
-        <v>0.661209247476497</v>
+        <v>-0.2562164671919351</v>
       </c>
       <c r="Q10">
-        <v>0.6634313117917857</v>
+        <v>0.1960755905500214</v>
       </c>
       <c r="R10">
-        <v>0.9966506490185285</v>
+        <v>-1.306722914735126</v>
       </c>
       <c r="S10">
-        <v>0.3189341120895131</v>
+        <v>0.1913068333598291</v>
       </c>
       <c r="X10">
-        <v>0.545689380305628</v>
+        <v>0.6208072650528155</v>
       </c>
       <c r="Y10">
-        <v>0.7404311876747184</v>
+        <v>0.6462393484669829</v>
       </c>
       <c r="Z10">
-        <v>0.7369886484918796</v>
+        <v>0.9606460308019037</v>
       </c>
       <c r="AA10">
-        <v>0.4611292525234175</v>
+        <v>0.3367301757687087</v>
       </c>
       <c r="AB10">
-        <v>-1.678386646077054</v>
+        <v>0.3152625050970427</v>
       </c>
       <c r="AC10">
-        <v>1.274428537969165</v>
+        <v>0.4973825754522981</v>
       </c>
       <c r="AD10">
-        <v>-1.316971957291232</v>
+        <v>0.6338430830841968</v>
       </c>
       <c r="AE10">
-        <v>0.1878480245778852</v>
+        <v>0.5261832333921048</v>
       </c>
     </row>
   </sheetData>
